--- a/data/2.b_Hybrider_Netzzugang_2025_3%/Power_VRES.xlsx
+++ b/data/2.b_Hybrider_Netzzugang_2025_3%/Power_VRES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\LEGO-Pyomo\data\2.b_Hybrider_Netzzugang_2025_3%\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1511E994-C20E-4F33-BEF5-1D8C72C7C9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B36C718-8DEC-4DEF-8248-641C03F7592E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9610" yWindow="1100" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="490" yWindow="2220" windowWidth="19580" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ScenarioA!$B$7:$Q$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ScenarioA!$B$7:$Q$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
   <si>
     <t>Power - Variable Renewable Energy Sources</t>
   </si>
@@ -378,10 +378,13 @@
     <t>PV_OW_15</t>
   </si>
   <si>
-    <t>PV_OW_35</t>
-  </si>
-  <si>
-    <t>PV_OW_70</t>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>PV_Track</t>
+  </si>
+  <si>
+    <t>0.002</t>
   </si>
 </sst>
 </file>
@@ -394,7 +397,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +429,12 @@
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -838,7 +847,7 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" customWidth="1"/>
@@ -1379,16 +1388,16 @@
         <v>1</v>
       </c>
       <c r="H11" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="13">
         <v>1000</v>
       </c>
       <c r="J11" s="15">
-        <v>34031</v>
-      </c>
-      <c r="K11" s="15">
-        <v>1</v>
+        <v>34694.422838514089</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="L11" s="16">
         <v>0</v>
@@ -1438,10 +1447,10 @@
         <v>1000</v>
       </c>
       <c r="J12" s="15">
-        <v>34031</v>
-      </c>
-      <c r="K12" s="15">
-        <v>1</v>
+        <v>34694.422838514089</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="L12" s="16">
         <v>0</v>
@@ -1470,7 +1479,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>72</v>
@@ -1485,16 +1494,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="13">
         <v>1000</v>
       </c>
       <c r="J13" s="15">
-        <v>34031</v>
-      </c>
-      <c r="K13" s="15">
-        <v>1</v>
+        <v>40837.406960820968</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="L13" s="16">
         <v>0</v>
@@ -1522,55 +1531,25 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19">
-        <v>1</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="15">
-        <v>34031</v>
-      </c>
-      <c r="K14" s="15">
-        <v>1</v>
-      </c>
-      <c r="L14" s="16">
-        <v>0</v>
-      </c>
-      <c r="M14" s="14">
-        <v>0</v>
-      </c>
-      <c r="N14" s="14">
-        <v>0</v>
-      </c>
-      <c r="O14" s="14">
-        <v>0</v>
-      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
-      <c r="T14" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="U14" s="18" t="s">
-        <v>77</v>
-      </c>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
@@ -2745,54 +2724,9 @@
       <c r="T65" s="18"/>
       <c r="U65" s="18"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="13"/>
-      <c r="Q66" s="13"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A67" s="10"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="13"/>
-      <c r="Q67" s="13"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B7:Q67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B7:Q65" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
